--- a/docs/overlap_decision_list.xlsx
+++ b/docs/overlap_decision_list.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overlap decisions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Genuine extras" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Αποφάσεις επικάλυψης" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Πράγματι πρόσθετες" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overlap decisions'!$A$1:$M$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Αποφάσεις επικάλυψης'!$A$1:$M$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,67 +456,67 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Service code</t>
+          <t>Κωδικός υπηρεσίας</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Τύπος</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Κατ.</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Service description (EL)</t>
+          <t>Περιγραφή υπηρεσίας</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Tariff code</t>
+          <t>Κωδικός τιμοκαταλόγου</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Tariff description (EL)</t>
+          <t>Περιγραφή τιμοκαταλόγου</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Tariff price (raw)</t>
+          <t>Τιμή (όπως δόθηκε)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Tariff price €</t>
+          <t>Τιμή €</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Πρόταση</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>RULING (fill in)</t>
+          <t>ΑΠΟΦΑΣΗ (συμπληρώστε)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Ruled by</t>
+          <t>Από</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Ruled on</t>
+          <t>Ημερομηνία</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Exposure €</t>
+          <t>Πρόσθετη χρέωση €</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
     <row r="44">
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Unruled pairs</t>
+          <t>Ζεύγη χωρίς απόφαση</t>
         </is>
       </c>
       <c r="J44" s="3">
@@ -2576,7 +2576,7 @@
     <row r="45">
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Exposure at current rulings €</t>
+          <t>Πρόσθετη χρέωση με τις τρέχουσες αποφάσεις €</t>
         </is>
       </c>
       <c r="J45" s="4">
@@ -2587,7 +2587,7 @@
     <row r="46">
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Exposure if all ruled 'both' €</t>
+          <t>Πρόσθετη χρέωση αν όλα κριθούν «both» €</t>
         </is>
       </c>
       <c r="J46" s="4">
@@ -2598,7 +2598,7 @@
   </sheetData>
   <autoFilter ref="A1:M42"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid ruling" error="Choose weight_only, tariff_only or both." type="list">
+    <dataValidation sqref="J2:J42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Μη έγκυρη απόφαση" error="Επιλέξτε weight_only, tariff_only ή both." type="list">
       <formula1>"weight_only,tariff_only,both"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2624,22 +2624,22 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Tariff code</t>
+          <t>Κωδικός</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>Description (EL)</t>
+          <t>Περιγραφή</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>Price (raw)</t>
+          <t>Τιμή (όπως δόθηκε)</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>Price €</t>
+          <t>Τιμή €</t>
         </is>
       </c>
     </row>
